--- a/ig/main/CodeSystem-terminologie-standardterms.xlsx
+++ b/ig/main/CodeSystem-terminologie-standardterms.xlsx
@@ -31,10 +31,10 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>OID:0.4.0.127.0.16.1.1.2.1 (use: usual, )</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/#terminologie-standardterms (use: secondary, )</t>
+    <t>OID:0.4.0.127.0.16.1.1.2.1 (use: usual)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/#terminologie-standardterms (use: secondary)</t>
   </si>
   <si>
     <t>Version</t>
